--- a/data/trans_orig/P32D_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P32D_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año en 2023</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9542</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171279</t>
+          <t>170376</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179199</t>
+          <t>179200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81141</t>
+          <t>82548</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90324</t>
+          <t>90347</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>258001</t>
+          <t>257147</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>268746</t>
+          <t>268361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19619</t>
+          <t>20296</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23825</t>
+          <t>22902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>236017</t>
+          <t>235340</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>251864</t>
+          <t>251638</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109406</t>
+          <t>110267</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348781</t>
+          <t>349704</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>367278</t>
+          <t>367128</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>8767</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24208</t>
+          <t>24380</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>24483</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>158687</t>
+          <t>158515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>174288</t>
+          <t>174128</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84997</t>
+          <t>83892</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248571</t>
+          <t>248224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>263613</t>
+          <t>263813</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24184</t>
+          <t>24389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18522</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>12256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34971</t>
+          <t>37027</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152536</t>
+          <t>152331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172274</t>
+          <t>172290</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>105097</t>
+          <t>104866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>118632</t>
+          <t>118486</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>265368</t>
+          <t>263312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>287501</t>
+          <t>288083</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>964</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23871</t>
+          <t>24089</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30533</t>
+          <t>30502</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31577</t>
+          <t>31972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38807</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19012</t>
+          <t>19147</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39159</t>
+          <t>39350</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13141</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25263</t>
+          <t>25328</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47963</t>
+          <t>45935</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125889</t>
+          <t>125698</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>146036</t>
+          <t>145901</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83279</t>
+          <t>84020</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>93052</t>
+          <t>93461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>213505</t>
+          <t>215533</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>236205</t>
+          <t>236140</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22874</t>
+          <t>22239</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45527</t>
+          <t>45821</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38447</t>
+          <t>36422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17273</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73847</t>
+          <t>74298</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>258319</t>
+          <t>258025</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>280972</t>
+          <t>281607</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>360010</t>
+          <t>362035</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>394878</t>
+          <t>395561</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>628456</t>
+          <t>628005</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>685030</t>
+          <t>683105</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30649</t>
+          <t>30694</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56363</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23520</t>
+          <t>24603</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45728</t>
+          <t>45486</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73927</t>
+          <t>74283</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>219502</t>
+          <t>218484</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>245216</t>
+          <t>245171</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76305</t>
+          <t>75222</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89637</t>
+          <t>89268</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>301762</t>
+          <t>301406</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>329961</t>
+          <t>330203</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>122651</t>
+          <t>122231</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>171136</t>
+          <t>171466</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28096</t>
+          <t>27570</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76684</t>
+          <t>76004</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>149926</t>
+          <t>147196</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>231208</t>
+          <t>231696</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1399908</t>
+          <t>1399578</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1448393</t>
+          <t>1448813</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>947684</t>
+          <t>948364</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>996272</t>
+          <t>996798</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2364205</t>
+          <t>2363717</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2445487</t>
+          <t>2448217</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32D_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P32D_R-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>8012</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>12469</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>177060</t>
+          <t>167218</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>170376</t>
+          <t>161887</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179200</t>
+          <t>169174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87965</t>
+          <t>93475</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82548</t>
+          <t>88793</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90347</t>
+          <t>96278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>265025</t>
+          <t>260693</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257147</t>
+          <t>254661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>268361</t>
+          <t>264470</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,102 +1068,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20296</t>
+          <t>20414</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6815</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>11797</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>5962</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>22422</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1885</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6703</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>12073</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>5478</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>22902</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -1181,102 +1181,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>245448</t>
+          <t>249863</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>235340</t>
+          <t>239442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>251638</t>
+          <t>255414</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>121079</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>116068</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>122883</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,45%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>370942</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>360317</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>376777</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>96,92%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>94,14%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>98,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>115085</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>110267</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>116970</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>94,27%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>360533</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>349704</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>367128</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>255636</t>
+          <t>259856</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>255636</t>
+          <t>259856</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>255636</t>
+          <t>259856</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>372606</t>
+          <t>382739</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>372606</t>
+          <t>382739</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>372606</t>
+          <t>382739</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24380</t>
+          <t>25145</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>944</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15987</t>
+          <t>17178</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>10065</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24483</t>
+          <t>25533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>167895</t>
+          <t>168975</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>158515</t>
+          <t>160065</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>174128</t>
+          <t>175796</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88825</t>
+          <t>87836</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83892</t>
+          <t>84016</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89812</t>
+          <t>88780</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>256720</t>
+          <t>256811</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248224</t>
+          <t>248456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>263813</t>
+          <t>263924</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>182895</t>
+          <t>185210</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>182895</t>
+          <t>185210</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>182895</t>
+          <t>185210</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>89812</t>
+          <t>88780</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89812</t>
+          <t>88780</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89812</t>
+          <t>88780</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>272707</t>
+          <t>273989</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>272707</t>
+          <t>273989</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>272707</t>
+          <t>273989</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24389</t>
+          <t>29259</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>11578</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>21398</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>21318</t>
+          <t>23423</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12256</t>
+          <t>13295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37027</t>
+          <t>39544</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>165713</t>
+          <t>190010</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152331</t>
+          <t>172596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172290</t>
+          <t>197184</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>113308</t>
+          <t>126059</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104866</t>
+          <t>116239</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>118486</t>
+          <t>131906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>279021</t>
+          <t>316069</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>263312</t>
+          <t>299948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>288083</t>
+          <t>326197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>176720</t>
+          <t>201855</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>176720</t>
+          <t>201855</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>176720</t>
+          <t>201855</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>123619</t>
+          <t>137637</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>123619</t>
+          <t>137637</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>123619</t>
+          <t>137637</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>300339</t>
+          <t>339492</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>300339</t>
+          <t>339492</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>300339</t>
+          <t>339492</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>849</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28590</t>
+          <t>31373</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24089</t>
+          <t>26861</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30502</t>
+          <t>33473</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,27 +2245,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>36629</t>
+          <t>41369</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31972</t>
+          <t>36245</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38765</t>
+          <t>43696</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27453</t>
+          <t>27288</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19147</t>
+          <t>19031</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39350</t>
+          <t>37261</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>13554</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>34495</t>
+          <t>34425</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25328</t>
+          <t>24829</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45935</t>
+          <t>45249</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>137595</t>
+          <t>135685</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125698</t>
+          <t>125712</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>145901</t>
+          <t>143942</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>89377</t>
+          <t>91057</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84020</t>
+          <t>84640</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>93461</t>
+          <t>94642</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>226973</t>
+          <t>226742</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>215533</t>
+          <t>215918</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>236140</t>
+          <t>236338</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>32954</t>
+          <t>43913</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22239</t>
+          <t>31808</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45821</t>
+          <t>62423</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36422</t>
+          <t>31512</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>48246</t>
+          <t>63560</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19198</t>
+          <t>47423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74298</t>
+          <t>83241</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>270892</t>
+          <t>302254</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>258025</t>
+          <t>283744</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>281607</t>
+          <t>314359</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>383166</t>
+          <t>213996</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>362035</t>
+          <t>202131</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>395561</t>
+          <t>221950</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>654057</t>
+          <t>516250</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>628005</t>
+          <t>496569</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>683105</t>
+          <t>532387</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>303846</t>
+          <t>346167</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>303846</t>
+          <t>346167</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>303846</t>
+          <t>346167</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>398457</t>
+          <t>233643</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>398457</t>
+          <t>233643</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>398457</t>
+          <t>233643</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>702303</t>
+          <t>579810</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>702303</t>
+          <t>579810</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>702303</t>
+          <t>579810</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>42122</t>
+          <t>46764</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30694</t>
+          <t>34083</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>62396</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>15936</t>
+          <t>18473</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>28061</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>58058</t>
+          <t>65236</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45486</t>
+          <t>50863</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>74283</t>
+          <t>83395</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>233743</t>
+          <t>265735</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>218484</t>
+          <t>250103</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>245171</t>
+          <t>278416</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>83889</t>
+          <t>96481</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>75222</t>
+          <t>86893</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89268</t>
+          <t>103132</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>317631</t>
+          <t>362217</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>301406</t>
+          <t>344058</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>330203</t>
+          <t>376590</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>275865</t>
+          <t>312499</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>275865</t>
+          <t>312499</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>275865</t>
+          <t>312499</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>375689</t>
+          <t>427453</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>375689</t>
+          <t>427453</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>375689</t>
+          <t>427453</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,69 +3469,69 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>144110</t>
+          <t>161482</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>122231</t>
+          <t>135843</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>171466</t>
+          <t>191270</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>11,44%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>64186</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>50900</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>82942</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
           <t>9,17%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>54715</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>27570</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>76004</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>213</t>
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>198824</t>
+          <t>225668</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>147196</t>
+          <t>197117</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>231696</t>
+          <t>259529</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -3582,67 +3582,67 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1426934</t>
+          <t>1511115</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1399578</t>
+          <t>1481327</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1448813</t>
+          <t>1536754</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>90,35%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>88,56%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>91,88%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1132</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>839979</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>821223</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>853265</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>90,83%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>89,09%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>92,22%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1132</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>969653</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>948364</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>996798</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>94,66%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>92,58%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2396589</t>
+          <t>2351094</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2363717</t>
+          <t>2317233</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2448217</t>
+          <t>2379645</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
